--- a/Data/MP_Exudate_age_230809.xlsx
+++ b/Data/MP_Exudate_age_230809.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chanceenglish/Desktop/Lab Shiz/ARPA-e/MP Exudate Sampling/data/Compiled Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chanceenglish/Desktop/Lab Shiz/ARPA-e/Giant_Kelp_DOC/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501BFA63-2911-B14F-9D08-60C35E0A2A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20BB9C1A-21E4-9240-B827-508C76C31398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="28800" windowHeight="17540" activeTab="2" xr2:uid="{01E47827-3DE7-2340-97AB-04E5D9FACEB0}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="3" xr2:uid="{01E47827-3DE7-2340-97AB-04E5D9FACEB0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="model" sheetId="10" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NPP_DOC_phys_env!$A$1:$Y$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NPP_DOC_phys_env!$A$1:$Y$217</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="92">
   <si>
     <t>date</t>
   </si>
@@ -8447,6 +8447,9 @@
       <c r="B2" t="s">
         <v>5</v>
       </c>
+      <c r="C2" t="s">
+        <v>87</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
@@ -8476,6 +8479,9 @@
       <c r="B3" t="s">
         <v>5</v>
       </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
       <c r="D3">
         <v>2</v>
       </c>
@@ -8505,6 +8511,9 @@
       <c r="B4" t="s">
         <v>5</v>
       </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
       <c r="D4">
         <v>3</v>
       </c>
@@ -8534,6 +8543,9 @@
       <c r="B5" t="s">
         <v>5</v>
       </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
       <c r="D5">
         <v>4</v>
       </c>
@@ -8563,6 +8575,9 @@
       <c r="B6" t="s">
         <v>5</v>
       </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
       <c r="D6">
         <v>5</v>
       </c>
@@ -8592,6 +8607,9 @@
       <c r="B7" t="s">
         <v>5</v>
       </c>
+      <c r="C7" t="s">
+        <v>87</v>
+      </c>
       <c r="D7">
         <v>6</v>
       </c>
@@ -8621,6 +8639,9 @@
       <c r="B8" t="s">
         <v>5</v>
       </c>
+      <c r="C8" t="s">
+        <v>87</v>
+      </c>
       <c r="D8">
         <v>1</v>
       </c>
@@ -8650,6 +8671,9 @@
       <c r="B9" t="s">
         <v>5</v>
       </c>
+      <c r="C9" t="s">
+        <v>87</v>
+      </c>
       <c r="D9">
         <v>2</v>
       </c>
@@ -8679,6 +8703,9 @@
       <c r="B10" t="s">
         <v>5</v>
       </c>
+      <c r="C10" t="s">
+        <v>87</v>
+      </c>
       <c r="D10">
         <v>3</v>
       </c>
@@ -8708,6 +8735,9 @@
       <c r="B11" t="s">
         <v>5</v>
       </c>
+      <c r="C11" t="s">
+        <v>87</v>
+      </c>
       <c r="D11">
         <v>4</v>
       </c>
@@ -8737,6 +8767,9 @@
       <c r="B12" t="s">
         <v>5</v>
       </c>
+      <c r="C12" t="s">
+        <v>87</v>
+      </c>
       <c r="D12">
         <v>5</v>
       </c>
@@ -8766,6 +8799,9 @@
       <c r="B13" t="s">
         <v>5</v>
       </c>
+      <c r="C13" t="s">
+        <v>87</v>
+      </c>
       <c r="D13">
         <v>6</v>
       </c>
@@ -8795,6 +8831,9 @@
       <c r="B14" t="s">
         <v>5</v>
       </c>
+      <c r="C14" t="s">
+        <v>87</v>
+      </c>
       <c r="D14">
         <v>1</v>
       </c>
@@ -8824,6 +8863,9 @@
       <c r="B15" t="s">
         <v>5</v>
       </c>
+      <c r="C15" t="s">
+        <v>87</v>
+      </c>
       <c r="D15">
         <v>2</v>
       </c>
@@ -8853,6 +8895,9 @@
       <c r="B16" t="s">
         <v>5</v>
       </c>
+      <c r="C16" t="s">
+        <v>87</v>
+      </c>
       <c r="D16">
         <v>3</v>
       </c>
@@ -8882,6 +8927,9 @@
       <c r="B17" t="s">
         <v>5</v>
       </c>
+      <c r="C17" t="s">
+        <v>87</v>
+      </c>
       <c r="D17">
         <v>4</v>
       </c>
@@ -8911,6 +8959,9 @@
       <c r="B18" t="s">
         <v>5</v>
       </c>
+      <c r="C18" t="s">
+        <v>87</v>
+      </c>
       <c r="D18">
         <v>5</v>
       </c>
@@ -8940,6 +8991,9 @@
       <c r="B19" t="s">
         <v>5</v>
       </c>
+      <c r="C19" t="s">
+        <v>87</v>
+      </c>
       <c r="D19">
         <v>6</v>
       </c>
@@ -15708,6 +15762,9 @@
       <c r="B110" t="s">
         <v>5</v>
       </c>
+      <c r="C110" t="s">
+        <v>86</v>
+      </c>
       <c r="D110">
         <v>1</v>
       </c>
@@ -15777,6 +15834,9 @@
       <c r="B111" t="s">
         <v>5</v>
       </c>
+      <c r="C111" t="s">
+        <v>86</v>
+      </c>
       <c r="D111">
         <v>2</v>
       </c>
@@ -15843,6 +15903,9 @@
       <c r="B112" t="s">
         <v>5</v>
       </c>
+      <c r="C112" t="s">
+        <v>86</v>
+      </c>
       <c r="D112">
         <v>3</v>
       </c>
@@ -15912,6 +15975,9 @@
       <c r="B113" t="s">
         <v>5</v>
       </c>
+      <c r="C113" t="s">
+        <v>86</v>
+      </c>
       <c r="D113">
         <v>4</v>
       </c>
@@ -15981,6 +16047,9 @@
       <c r="B114" t="s">
         <v>5</v>
       </c>
+      <c r="C114" t="s">
+        <v>86</v>
+      </c>
       <c r="D114">
         <v>5</v>
       </c>
@@ -16050,6 +16119,9 @@
       <c r="B115" t="s">
         <v>5</v>
       </c>
+      <c r="C115" t="s">
+        <v>86</v>
+      </c>
       <c r="D115">
         <v>6</v>
       </c>
@@ -16119,6 +16191,9 @@
       <c r="B116" t="s">
         <v>5</v>
       </c>
+      <c r="C116" t="s">
+        <v>86</v>
+      </c>
       <c r="D116">
         <v>1</v>
       </c>
@@ -16188,6 +16263,9 @@
       <c r="B117" t="s">
         <v>5</v>
       </c>
+      <c r="C117" t="s">
+        <v>86</v>
+      </c>
       <c r="D117">
         <v>2</v>
       </c>
@@ -16257,6 +16335,9 @@
       <c r="B118" t="s">
         <v>5</v>
       </c>
+      <c r="C118" t="s">
+        <v>86</v>
+      </c>
       <c r="D118">
         <v>3</v>
       </c>
@@ -16326,6 +16407,9 @@
       <c r="B119" t="s">
         <v>5</v>
       </c>
+      <c r="C119" t="s">
+        <v>86</v>
+      </c>
       <c r="D119">
         <v>4</v>
       </c>
@@ -16395,6 +16479,9 @@
       <c r="B120" t="s">
         <v>5</v>
       </c>
+      <c r="C120" t="s">
+        <v>86</v>
+      </c>
       <c r="D120">
         <v>5</v>
       </c>
@@ -16464,6 +16551,9 @@
       <c r="B121" t="s">
         <v>5</v>
       </c>
+      <c r="C121" t="s">
+        <v>86</v>
+      </c>
       <c r="D121">
         <v>6</v>
       </c>
@@ -16533,6 +16623,9 @@
       <c r="B122" t="s">
         <v>5</v>
       </c>
+      <c r="C122" t="s">
+        <v>86</v>
+      </c>
       <c r="D122">
         <v>1</v>
       </c>
@@ -16602,6 +16695,9 @@
       <c r="B123" t="s">
         <v>5</v>
       </c>
+      <c r="C123" t="s">
+        <v>86</v>
+      </c>
       <c r="D123">
         <v>2</v>
       </c>
@@ -16671,6 +16767,9 @@
       <c r="B124" t="s">
         <v>5</v>
       </c>
+      <c r="C124" t="s">
+        <v>86</v>
+      </c>
       <c r="D124">
         <v>3</v>
       </c>
@@ -16740,6 +16839,9 @@
       <c r="B125" t="s">
         <v>5</v>
       </c>
+      <c r="C125" t="s">
+        <v>86</v>
+      </c>
       <c r="D125">
         <v>4</v>
       </c>
@@ -16809,6 +16911,9 @@
       <c r="B126" t="s">
         <v>5</v>
       </c>
+      <c r="C126" t="s">
+        <v>86</v>
+      </c>
       <c r="D126">
         <v>5</v>
       </c>
@@ -16878,6 +16983,9 @@
       <c r="B127" t="s">
         <v>5</v>
       </c>
+      <c r="C127" t="s">
+        <v>86</v>
+      </c>
       <c r="D127">
         <v>6</v>
       </c>
@@ -16947,6 +17055,9 @@
       <c r="B128" t="s">
         <v>81</v>
       </c>
+      <c r="C128" t="s">
+        <v>86</v>
+      </c>
       <c r="D128">
         <v>1</v>
       </c>
@@ -17010,6 +17121,9 @@
       <c r="B129" t="s">
         <v>81</v>
       </c>
+      <c r="C129" t="s">
+        <v>86</v>
+      </c>
       <c r="D129">
         <v>2</v>
       </c>
@@ -17034,6 +17148,9 @@
       <c r="B130" t="s">
         <v>81</v>
       </c>
+      <c r="C130" t="s">
+        <v>86</v>
+      </c>
       <c r="D130">
         <v>3</v>
       </c>
@@ -17097,6 +17214,9 @@
       <c r="B131" t="s">
         <v>81</v>
       </c>
+      <c r="C131" t="s">
+        <v>86</v>
+      </c>
       <c r="D131">
         <v>4</v>
       </c>
@@ -17160,6 +17280,9 @@
       <c r="B132" t="s">
         <v>81</v>
       </c>
+      <c r="C132" t="s">
+        <v>86</v>
+      </c>
       <c r="D132">
         <v>5</v>
       </c>
@@ -17223,6 +17346,9 @@
       <c r="B133" t="s">
         <v>81</v>
       </c>
+      <c r="C133" t="s">
+        <v>86</v>
+      </c>
       <c r="D133">
         <v>6</v>
       </c>
@@ -17286,6 +17412,9 @@
       <c r="B134" t="s">
         <v>81</v>
       </c>
+      <c r="C134" t="s">
+        <v>86</v>
+      </c>
       <c r="D134">
         <v>1</v>
       </c>
@@ -17349,6 +17478,9 @@
       <c r="B135" t="s">
         <v>81</v>
       </c>
+      <c r="C135" t="s">
+        <v>86</v>
+      </c>
       <c r="D135">
         <v>2</v>
       </c>
@@ -17373,6 +17505,9 @@
       <c r="B136" t="s">
         <v>81</v>
       </c>
+      <c r="C136" t="s">
+        <v>86</v>
+      </c>
       <c r="D136">
         <v>3</v>
       </c>
@@ -17436,6 +17571,9 @@
       <c r="B137" t="s">
         <v>81</v>
       </c>
+      <c r="C137" t="s">
+        <v>86</v>
+      </c>
       <c r="D137">
         <v>4</v>
       </c>
@@ -17499,6 +17637,9 @@
       <c r="B138" t="s">
         <v>81</v>
       </c>
+      <c r="C138" t="s">
+        <v>86</v>
+      </c>
       <c r="D138">
         <v>5</v>
       </c>
@@ -17562,6 +17703,9 @@
       <c r="B139" t="s">
         <v>81</v>
       </c>
+      <c r="C139" t="s">
+        <v>86</v>
+      </c>
       <c r="D139">
         <v>6</v>
       </c>
@@ -17625,6 +17769,9 @@
       <c r="B140" t="s">
         <v>81</v>
       </c>
+      <c r="C140" t="s">
+        <v>86</v>
+      </c>
       <c r="D140">
         <v>1</v>
       </c>
@@ -17688,6 +17835,9 @@
       <c r="B141" t="s">
         <v>81</v>
       </c>
+      <c r="C141" t="s">
+        <v>86</v>
+      </c>
       <c r="D141">
         <v>2</v>
       </c>
@@ -17712,6 +17862,9 @@
       <c r="B142" t="s">
         <v>81</v>
       </c>
+      <c r="C142" t="s">
+        <v>86</v>
+      </c>
       <c r="D142">
         <v>3</v>
       </c>
@@ -17775,6 +17928,9 @@
       <c r="B143" t="s">
         <v>81</v>
       </c>
+      <c r="C143" t="s">
+        <v>86</v>
+      </c>
       <c r="D143">
         <v>4</v>
       </c>
@@ -17838,6 +17994,9 @@
       <c r="B144" t="s">
         <v>81</v>
       </c>
+      <c r="C144" t="s">
+        <v>86</v>
+      </c>
       <c r="D144">
         <v>5</v>
       </c>
@@ -17901,6 +18060,9 @@
       <c r="B145" t="s">
         <v>81</v>
       </c>
+      <c r="C145" t="s">
+        <v>86</v>
+      </c>
       <c r="D145">
         <v>6</v>
       </c>
@@ -22710,7 +22872,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y145" xr:uid="{49CD9F5B-F78E-4A43-83E2-632B4C6A9FC8}"/>
+  <autoFilter ref="A1:Y217" xr:uid="{49CD9F5B-F78E-4A43-83E2-632B4C6A9FC8}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
